--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260529_213203.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260529_213203.xlsx
@@ -6344,7 +6344,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260529_213203.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260529_213203.xlsx
@@ -6344,7 +6344,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
